--- a/public/exports-with-coowners/29189579.xlsx
+++ b/public/exports-with-coowners/29189579.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/29189579.xlsx
+++ b/public/exports-with-coowners/29189579.xlsx
@@ -7789,7 +7789,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039780</t>
+          <t xml:space="preserve">200039782</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9154,12 +9154,12 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports-with-coowners/29189579.xlsx
+++ b/public/exports-with-coowners/29189579.xlsx
@@ -7789,7 +7789,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039782</t>
+          <t xml:space="preserve">200039780</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9304,12 +9304,12 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -9379,12 +9379,12 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
